--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20232.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -97,22 +106,52 @@
     <t>NIEVES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
+  </si>
+  <si>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
+    <t>AYLIN MELISSA</t>
   </si>
   <si>
     <t>LUIS EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
   </si>
 </sst>
 </file>
@@ -682,16 +721,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -705,16 +747,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -728,16 +773,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -751,16 +799,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80.77</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -774,16 +825,19 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>73.33</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +902,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -865,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>91.67</v>
+        <v>79.17</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -891,16 +945,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>89.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -917,16 +971,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>84.62</v>
+        <v>80.77</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -943,16 +997,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>86.67</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -994,16 +1048,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920162</v>
+        <v>21330051920176</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1017,22 +1071,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920176</v>
+        <v>21330051920334</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1040,16 +1094,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920314</v>
+        <v>21330051920125</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1063,24 +1117,162 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920003</v>
+        <v>21330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920069</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920003</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920335</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20232.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,79 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
   </si>
 </sst>
 </file>
@@ -893,16 +836,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -919,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>79.17</v>
+        <v>95.83</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -945,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -971,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>80.77</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -997,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1048,16 +991,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920176</v>
+        <v>21330051920164</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,209 +1014,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920334</v>
+        <v>21330051920203</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920125</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920190</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920162</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920069</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920335</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920137</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920122</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
